--- a/tools/fixtures/po-import-sample.xlsx
+++ b/tools/fixtures/po-import-sample.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">Widget X — phase-12-7 fixture</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-27</t>
+    <t xml:space="preserve">27/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ORD-A-1</t>

--- a/tools/fixtures/po-import-sample.xlsx
+++ b/tools/fixtures/po-import-sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t xml:space="preserve">PULL SHEET ID / PRS NO</t>
   </si>
@@ -41,6 +41,9 @@
     <t xml:space="preserve">PALLET ID</t>
   </si>
   <si>
+    <t xml:space="preserve">PO</t>
+  </si>
+  <si>
     <t xml:space="preserve">P127TEST-001</t>
   </si>
   <si>
@@ -56,7 +59,7 @@
     <t xml:space="preserve">Widget X — phase-12-7 fixture</t>
   </si>
   <si>
-    <t xml:space="preserve">27/05/2026</t>
+    <t xml:space="preserve">09/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">ORD-A-1</t>
@@ -65,6 +68,9 @@
     <t xml:space="preserve">PAL-A-1</t>
   </si>
   <si>
+    <t xml:space="preserve">TH5805-A001</t>
+  </si>
+  <si>
     <t xml:space="preserve">TST-WIDGET-002</t>
   </si>
   <si>
@@ -77,6 +83,9 @@
     <t xml:space="preserve">PAL-A-2</t>
   </si>
   <si>
+    <t xml:space="preserve">TH5805-A002</t>
+  </si>
+  <si>
     <t xml:space="preserve">P127TEST-002</t>
   </si>
   <si>
@@ -98,6 +107,9 @@
     <t xml:space="preserve">PAL-B-1</t>
   </si>
   <si>
+    <t xml:space="preserve">TH5805-B001</t>
+  </si>
+  <si>
     <t xml:space="preserve">TST-GIZMO-002</t>
   </si>
   <si>
@@ -108,6 +120,9 @@
   </si>
   <si>
     <t xml:space="preserve">PAL-B-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH5805-B002</t>
   </si>
 </sst>
 </file>
@@ -152,7 +167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -183,121 +198,136 @@
       <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="0">
         <v>12</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="0">
         <v>24</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" s="0">
         <v>6</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F5" s="0">
         <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
